--- a/exemplos_para_envio/ALTERADA - B2 Primavera 09-2026.xlsx
+++ b/exemplos_para_envio/ALTERADA - B2 Primavera 09-2026.xlsx
@@ -13,9 +13,9 @@
     <sheet name="DESPESAS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3720,8 +3720,344 @@
         <v>6.69</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>20984</v>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E110" s="9" t="n">
+        <v>5210</v>
+      </c>
+      <c r="F110" s="9" t="n">
+        <v>50721</v>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>5.748</v>
+      </c>
+      <c r="H110" s="11" t="n">
+        <v>6.185</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C111" s="13" t="n">
+        <v>3606</v>
+      </c>
+      <c r="D111" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E111" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>12330</v>
+      </c>
+      <c r="G111" s="14" t="n">
+        <v>5.8987</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>6.679</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="n">
+        <v>25872</v>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="9" t="n">
+        <v>2630</v>
+      </c>
+      <c r="F112" s="9" t="n">
+        <v>23239</v>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>3.992</v>
+      </c>
+      <c r="H112" s="11" t="n">
+        <v>4.483</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C113" s="13" t="n">
+        <v>11875</v>
+      </c>
+      <c r="D113" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="13" t="n">
+        <v>1824</v>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>10049</v>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>6.0675</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>6.683</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>50721</v>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>5071</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>45605</v>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>5.748</v>
+      </c>
+      <c r="H114" s="11" t="n">
+        <v>6.181</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C115" s="13" t="n">
+        <v>12330</v>
+      </c>
+      <c r="D115" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="13" t="n">
+        <v>1206</v>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>11122</v>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>5.8987</v>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>6.685</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>23239</v>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="9" t="n">
+        <v>2659</v>
+      </c>
+      <c r="F116" s="9" t="n">
+        <v>20578</v>
+      </c>
+      <c r="G116" s="10" t="n">
+        <v>3.992</v>
+      </c>
+      <c r="H116" s="11" t="n">
+        <v>4.479</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C117" s="13" t="n">
+        <v>10049</v>
+      </c>
+      <c r="D117" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="13" t="n">
+        <v>1552</v>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>8495</v>
+      </c>
+      <c r="G117" s="14" t="n">
+        <v>6.0675</v>
+      </c>
+      <c r="H117" s="15" t="n">
+        <v>6.684</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="n">
+        <v>45605</v>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="9" t="n">
+        <v>4928</v>
+      </c>
+      <c r="F118" s="9" t="n">
+        <v>40630</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>5.748</v>
+      </c>
+      <c r="H118" s="11" t="n">
+        <v>6.183</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C119" s="13" t="n">
+        <v>11122</v>
+      </c>
+      <c r="D119" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="13" t="n">
+        <v>1248</v>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>9874</v>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>5.8987</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>6.681</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>20578</v>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="9" t="n">
+        <v>2613</v>
+      </c>
+      <c r="F120" s="9" t="n">
+        <v>17961</v>
+      </c>
+      <c r="G120" s="10" t="n">
+        <v>3.992</v>
+      </c>
+      <c r="H120" s="11" t="n">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C121" s="13" t="n">
+        <v>8495</v>
+      </c>
+      <c r="D121" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="13" t="n">
+        <v>1626</v>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>6868</v>
+      </c>
+      <c r="G121" s="14" t="n">
+        <v>6.0675</v>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>6.685</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H109"/>
+  <autoFilter ref="A1:H121"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>
@@ -3737,7 +4073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4245,8 +4581,62 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>35000</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>5.7384</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>200845.74</v>
+      </c>
+      <c r="F19" t="n">
+        <v>212121</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Distribuidora Paraná</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>5.8961</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>58961.07</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>212154</v>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Distribuidora Sul</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G20"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>
@@ -4262,7 +4652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4295,92 +4685,92 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1454.41</v>
+        <v>57825.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1124.97</v>
+        <v>2067.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>57557.61</v>
+        <v>3712.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3465.79</v>
+        <v>2677.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>2891.12</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="7">
@@ -4389,52 +4779,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>14000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>3600</v>
+        <v>1067.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>2392.7</v>
+        <v>1486.15</v>
       </c>
     </row>
     <row r="10">
@@ -4452,7 +4842,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1111.06</v>
+        <v>1077.07</v>
       </c>
     </row>
     <row r="11">
@@ -4470,7 +4860,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>3943.17</v>
+        <v>3912.76</v>
       </c>
     </row>
     <row r="12">
@@ -4488,7 +4878,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>8979.440000000001</v>
+        <v>8973.01</v>
       </c>
     </row>
     <row r="13">
@@ -4506,25 +4896,25 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>3303.56</v>
+        <v>3593.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>20020.04</v>
+        <v>1333.94</v>
       </c>
     </row>
     <row r="15">
@@ -4533,34 +4923,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>3754.68</v>
+        <v>19985.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46290</v>
+        <v>46285</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1362.34</v>
+        <v>3811.43</v>
       </c>
     </row>
     <row r="17">
@@ -4578,11 +4968,29 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3767.17</v>
+        <v>3701.59</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Taxas de cartão</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Taxas das maquininhas (semana)</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>1525.3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D17"/>
+  <autoFilter ref="A1:D18"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Folha de pagamento,Aluguel,Energia elétrica,Água e esgoto,Taxas de cartão,Manutenção,Fretes,Sistemas e contabilidade,Marketing,Outras despesas"</formula1>
